--- a/Log Template.xlsx
+++ b/Log Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213372C1-B30C-4540-B5DB-535A84E6053B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD22769B-E7AC-4E56-BC27-3FF9D551B570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>DAILY MAINTENANCE TECHNICIAN LOG</t>
   </si>
@@ -94,9 +94,6 @@
   </si>
   <si>
     <t>Remarks</t>
-  </si>
-  <si>
-    <t>Test job</t>
   </si>
 </sst>
 </file>
@@ -481,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.6328125" customWidth="1"/>
@@ -616,7 +613,10 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="35.15" customHeight="1">
-      <c r="A5" s="5"/>
+      <c r="A5" s="5" t="str">
+        <f t="shared" ref="A5:A20" si="0">IF(D5="","",ROW()-4)</f>
+        <v/>
+      </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -627,14 +627,20 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
-      <c r="L5" s="7"/>
+      <c r="L5" s="7" t="str">
+        <f t="shared" ref="L5:L20" si="1">IF(OR(J5="",K5=""),"",ROUND(MOD(K5-J5,1)*24,2))</f>
+        <v/>
+      </c>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="1:16" ht="35.15" customHeight="1">
-      <c r="A6" s="5"/>
+      <c r="A6" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -645,14 +651,20 @@
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
-      <c r="L6" s="7"/>
+      <c r="L6" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="1:16" ht="35.15" customHeight="1">
-      <c r="A7" s="5"/>
+      <c r="A7" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -663,17 +675,18 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
+      <c r="L7" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
-      <c r="P7" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="P7" s="5"/>
     </row>
     <row r="8" spans="1:16" ht="35.15" customHeight="1">
       <c r="A8" s="5" t="str">
-        <f t="shared" ref="A5:A23" si="0">IF(D8="","",ROW()-4)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="B8" s="5"/>
@@ -687,7 +700,7 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="7" t="str">
-        <f t="shared" ref="L5:L23" si="1">IF(OR(J8="",K8=""),"",ROUND(MOD(K8-J8,1)*24,2))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M8" s="5"/>
@@ -983,84 +996,12 @@
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
     </row>
-    <row r="21" spans="1:16" ht="35.15" customHeight="1">
-      <c r="A21" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-    </row>
-    <row r="22" spans="1:16" ht="35.15" customHeight="1">
-      <c r="A22" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-    </row>
-    <row r="23" spans="1:16" ht="35.15" customHeight="1">
-      <c r="A23" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:P2"/>
     <mergeCell ref="A3:B3"/>
   </mergeCells>
-  <conditionalFormatting sqref="N5:N23">
+  <conditionalFormatting sqref="N5:N20">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>N5="Completed"</formula>
     </cfRule>
@@ -1072,13 +1013,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G5:G23" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G5:G20" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"AC / HVAC,Plumbing,Electrical,Civil / Painting,Fire &amp; Life Safety,Carpentry,General Maintenance,PPM,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H5:H23" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H5:H20" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Emergency,High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N5:N23" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N5:N20" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Completed,Pending,In Progress,On Hold"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Log Template.xlsx
+++ b/Log Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD22769B-E7AC-4E56-BC27-3FF9D551B570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82084B85-9D17-4E7F-BD3C-DA98C77CFF97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -614,7 +614,7 @@
     </row>
     <row r="5" spans="1:16" ht="35.15" customHeight="1">
       <c r="A5" s="5" t="str">
-        <f t="shared" ref="A5:A20" si="0">IF(D5="","",ROW()-4)</f>
+        <f>IF(D5="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B5" s="5"/>
@@ -628,7 +628,7 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="7" t="str">
-        <f t="shared" ref="L5:L20" si="1">IF(OR(J5="",K5=""),"",ROUND(MOD(K5-J5,1)*24,2))</f>
+        <f t="shared" ref="L5:L20" si="0">IF(OR(J5="",K5=""),"",ROUND(MOD(K5-J5,1)*24,2))</f>
         <v/>
       </c>
       <c r="M5" s="5"/>
@@ -637,10 +637,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="1:16" ht="35.15" customHeight="1">
-      <c r="A6" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -652,7 +649,7 @@
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
       <c r="L6" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M6" s="5"/>
@@ -662,7 +659,7 @@
     </row>
     <row r="7" spans="1:16" ht="35.15" customHeight="1">
       <c r="A7" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A5:A20" si="1">IF(D7="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B7" s="5"/>
@@ -676,7 +673,7 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
       <c r="L7" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M7" s="5"/>
@@ -686,7 +683,7 @@
     </row>
     <row r="8" spans="1:16" ht="35.15" customHeight="1">
       <c r="A8" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="B8" s="5"/>
@@ -700,7 +697,7 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M8" s="5"/>
@@ -710,7 +707,7 @@
     </row>
     <row r="9" spans="1:16" ht="35.15" customHeight="1">
       <c r="A9" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="B9" s="5"/>
@@ -724,7 +721,7 @@
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M9" s="5"/>
@@ -734,7 +731,7 @@
     </row>
     <row r="10" spans="1:16" ht="35.15" customHeight="1">
       <c r="A10" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="B10" s="5"/>
@@ -748,7 +745,7 @@
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M10" s="5"/>
@@ -758,7 +755,7 @@
     </row>
     <row r="11" spans="1:16" ht="35.15" customHeight="1">
       <c r="A11" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="B11" s="5"/>
@@ -772,7 +769,7 @@
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
       <c r="L11" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M11" s="5"/>
@@ -782,7 +779,7 @@
     </row>
     <row r="12" spans="1:16" ht="35.15" customHeight="1">
       <c r="A12" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="B12" s="5"/>
@@ -796,7 +793,7 @@
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
       <c r="L12" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M12" s="5"/>
@@ -806,7 +803,7 @@
     </row>
     <row r="13" spans="1:16" ht="35.15" customHeight="1">
       <c r="A13" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="B13" s="5"/>
@@ -820,7 +817,7 @@
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
       <c r="L13" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M13" s="5"/>
@@ -830,7 +827,7 @@
     </row>
     <row r="14" spans="1:16" ht="35.15" customHeight="1">
       <c r="A14" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="B14" s="5"/>
@@ -844,7 +841,7 @@
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
       <c r="L14" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M14" s="5"/>
@@ -854,7 +851,7 @@
     </row>
     <row r="15" spans="1:16" ht="35.15" customHeight="1">
       <c r="A15" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="B15" s="5"/>
@@ -868,7 +865,7 @@
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
       <c r="L15" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M15" s="5"/>
@@ -878,7 +875,7 @@
     </row>
     <row r="16" spans="1:16" ht="35.15" customHeight="1">
       <c r="A16" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="B16" s="5"/>
@@ -892,7 +889,7 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
       <c r="L16" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M16" s="5"/>
@@ -902,7 +899,7 @@
     </row>
     <row r="17" spans="1:16" ht="35.15" customHeight="1">
       <c r="A17" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="B17" s="5"/>
@@ -916,7 +913,7 @@
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
       <c r="L17" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M17" s="5"/>
@@ -926,7 +923,7 @@
     </row>
     <row r="18" spans="1:16" ht="35.15" customHeight="1">
       <c r="A18" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="B18" s="5"/>
@@ -940,7 +937,7 @@
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
       <c r="L18" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M18" s="5"/>
@@ -950,7 +947,7 @@
     </row>
     <row r="19" spans="1:16" ht="35.15" customHeight="1">
       <c r="A19" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="B19" s="5"/>
@@ -964,7 +961,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
       <c r="L19" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M19" s="5"/>
@@ -974,7 +971,7 @@
     </row>
     <row r="20" spans="1:16" ht="35.15" customHeight="1">
       <c r="A20" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="B20" s="5"/>
@@ -988,7 +985,7 @@
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="L20" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M20" s="5"/>
@@ -1012,7 +1009,7 @@
       <formula>N5="In Progress"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G5:G20" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"AC / HVAC,Plumbing,Electrical,Civil / Painting,Fire &amp; Life Safety,Carpentry,General Maintenance,PPM,Other"</formula1>
     </dataValidation>
